--- a/MaterialApi/Data/Chemical_Lab_Data.xlsx
+++ b/MaterialApi/Data/Chemical_Lab_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\BDL\MaterialApi\MaterialApi\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\BDL\MaterialApi\MaterialApi\bin\Debug\net8.0\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1639E327-B09D-42CF-BDAA-CB865BC5A798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB66DFA6-1F9D-4A52-BEFE-DDB7BE96CB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="2655" windowWidth="21600" windowHeight="11385" xr2:uid="{89A87849-3474-4FB3-9475-9E1F8DE40F30}"/>
+    <workbookView xWindow="2685" yWindow="5760" windowWidth="21600" windowHeight="11385" xr2:uid="{89A87849-3474-4FB3-9475-9E1F8DE40F30}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Assignment ID</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>Chemical Status</t>
+  </si>
+  <si>
+    <t>Vendor</t>
   </si>
 </sst>
 </file>
@@ -116,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -130,6 +133,14 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{888185CA-3822-4545-9033-9AE8F68FA681}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -458,7 +469,7 @@
     <col min="14" max="14" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -507,32 +518,41 @@
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O2" s="7"/>
+      <c r="P2" s="8"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O3" s="7"/>
+      <c r="P3" s="8"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O4" s="7"/>
+      <c r="P4" s="8"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="3"/>
@@ -540,7 +560,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="4"/>
@@ -548,7 +568,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="1"/>
@@ -556,7 +576,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -564,42 +584,42 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="F16" s="1"/>
